--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194948</v>
+        <v>125194965</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>96227</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,43 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592721</v>
+        <v>592758</v>
       </c>
       <c r="R2" t="n">
-        <v>6984921</v>
+        <v>6984821</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -756,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194963</v>
+        <v>125194946</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592734</v>
+        <v>592735</v>
       </c>
       <c r="R3" t="n">
-        <v>6984760</v>
+        <v>6984754</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -889,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194950</v>
+        <v>125194959</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>91410</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,42 +895,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592775</v>
+        <v>592555</v>
       </c>
       <c r="R4" t="n">
-        <v>6984833</v>
+        <v>6984742</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194964</v>
+        <v>125194963</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1039,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592722</v>
+        <v>592734</v>
       </c>
       <c r="R5" t="n">
-        <v>6984773</v>
+        <v>6984760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1101,10 +1078,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194959</v>
+        <v>125194960</v>
       </c>
       <c r="B6" t="n">
-        <v>91410</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1117,29 +1094,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>102612</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592555</v>
+        <v>592598</v>
       </c>
       <c r="R6" t="n">
-        <v>6984742</v>
+        <v>6984734</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1198,10 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194960</v>
+        <v>125194954</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1214,46 +1208,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592598</v>
+        <v>592687</v>
       </c>
       <c r="R7" t="n">
-        <v>6984734</v>
+        <v>6984736</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1312,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194946</v>
+        <v>125194952</v>
       </c>
       <c r="B8" t="n">
-        <v>74901</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,25 +1306,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1334,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592735</v>
+        <v>592763</v>
       </c>
       <c r="R8" t="n">
-        <v>6984754</v>
+        <v>6984830</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1414,10 +1396,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194965</v>
+        <v>125194961</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1426,25 +1408,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1436,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592758</v>
+        <v>592738</v>
       </c>
       <c r="R9" t="n">
-        <v>6984821</v>
+        <v>6984923</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1516,10 +1498,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194961</v>
+        <v>125194950</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,34 +1514,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592738</v>
+        <v>592775</v>
       </c>
       <c r="R10" t="n">
-        <v>6984923</v>
+        <v>6984833</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194952</v>
+        <v>125194957</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>79927</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592763</v>
+        <v>592680</v>
       </c>
       <c r="R11" t="n">
-        <v>6984830</v>
+        <v>6984734</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194954</v>
+        <v>125194948</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,34 +1726,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592687</v>
+        <v>592721</v>
       </c>
       <c r="R12" t="n">
-        <v>6984736</v>
+        <v>6984921</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1796,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194957</v>
+        <v>125194964</v>
       </c>
       <c r="B13" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592680</v>
+        <v>592722</v>
       </c>
       <c r="R13" t="n">
-        <v>6984734</v>
+        <v>6984773</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194965</v>
+        <v>125194963</v>
       </c>
       <c r="B2" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592758</v>
+        <v>592734</v>
       </c>
       <c r="R2" t="n">
-        <v>6984821</v>
+        <v>6984760</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194946</v>
+        <v>125194948</v>
       </c>
       <c r="B3" t="n">
-        <v>74901</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592735</v>
+        <v>592721</v>
       </c>
       <c r="R3" t="n">
-        <v>6984754</v>
+        <v>6984921</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194959</v>
+        <v>125194954</v>
       </c>
       <c r="B4" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,16 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592555</v>
+        <v>592687</v>
       </c>
       <c r="R4" t="n">
-        <v>6984742</v>
+        <v>6984736</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -976,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194963</v>
+        <v>125194961</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>91030</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -992,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592734</v>
+        <v>592738</v>
       </c>
       <c r="R5" t="n">
-        <v>6984760</v>
+        <v>6984923</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1078,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194960</v>
+        <v>125194950</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1094,33 +1109,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1130,10 +1141,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592598</v>
+        <v>592775</v>
       </c>
       <c r="R6" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1192,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194954</v>
+        <v>125194959</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>91410</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1208,21 +1219,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1232,10 +1238,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592687</v>
+        <v>592555</v>
       </c>
       <c r="R7" t="n">
-        <v>6984736</v>
+        <v>6984742</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1294,10 +1300,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194952</v>
+        <v>125194964</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1306,25 +1312,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1334,10 +1340,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592763</v>
+        <v>592722</v>
       </c>
       <c r="R8" t="n">
-        <v>6984830</v>
+        <v>6984773</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1396,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194961</v>
+        <v>125194965</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>96227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1408,25 +1414,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1436,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592738</v>
+        <v>592758</v>
       </c>
       <c r="R9" t="n">
-        <v>6984923</v>
+        <v>6984821</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1498,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194950</v>
+        <v>125194957</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1510,46 +1516,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592775</v>
+        <v>592680</v>
       </c>
       <c r="R10" t="n">
-        <v>6984833</v>
+        <v>6984734</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1608,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194957</v>
+        <v>125194960</v>
       </c>
       <c r="B11" t="n">
-        <v>79927</v>
+        <v>56714</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,35 +1618,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592680</v>
+        <v>592598</v>
       </c>
       <c r="R11" t="n">
         <v>6984734</v>
@@ -1710,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194948</v>
+        <v>125194946</v>
       </c>
       <c r="B12" t="n">
-        <v>57513</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,39 +1736,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592721</v>
+        <v>592735</v>
       </c>
       <c r="R12" t="n">
-        <v>6984921</v>
+        <v>6984754</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1791,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194964</v>
+        <v>125194952</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>96979</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592722</v>
+        <v>592763</v>
       </c>
       <c r="R13" t="n">
-        <v>6984773</v>
+        <v>6984830</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194963</v>
+        <v>125194960</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,46 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592734</v>
+        <v>592598</v>
       </c>
       <c r="R2" t="n">
-        <v>6984760</v>
+        <v>6984734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194948</v>
+        <v>125194950</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +805,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592721</v>
+        <v>592775</v>
       </c>
       <c r="R3" t="n">
-        <v>6984921</v>
+        <v>6984833</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -858,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194954</v>
+        <v>125194961</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592687</v>
+        <v>592738</v>
       </c>
       <c r="R4" t="n">
-        <v>6984736</v>
+        <v>6984923</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -991,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194961</v>
+        <v>125194952</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>96979</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1013,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592738</v>
+        <v>592763</v>
       </c>
       <c r="R5" t="n">
-        <v>6984923</v>
+        <v>6984830</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194950</v>
+        <v>125194946</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>74901</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,42 +1119,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592775</v>
+        <v>592735</v>
       </c>
       <c r="R6" t="n">
-        <v>6984833</v>
+        <v>6984754</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1203,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194959</v>
+        <v>125194964</v>
       </c>
       <c r="B7" t="n">
-        <v>91410</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1219,16 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1238,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592555</v>
+        <v>592722</v>
       </c>
       <c r="R7" t="n">
-        <v>6984742</v>
+        <v>6984773</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1300,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194964</v>
+        <v>125194965</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>96227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1312,25 +1319,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592722</v>
+        <v>592758</v>
       </c>
       <c r="R8" t="n">
-        <v>6984773</v>
+        <v>6984821</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1402,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194965</v>
+        <v>125194963</v>
       </c>
       <c r="B9" t="n">
-        <v>96227</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1414,25 +1421,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1442,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592758</v>
+        <v>592734</v>
       </c>
       <c r="R9" t="n">
-        <v>6984821</v>
+        <v>6984760</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1504,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194957</v>
+        <v>125194948</v>
       </c>
       <c r="B10" t="n">
-        <v>79927</v>
+        <v>57513</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,38 +1523,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592680</v>
+        <v>592721</v>
       </c>
       <c r="R10" t="n">
-        <v>6984734</v>
+        <v>6984921</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1580,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1606,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194960</v>
+        <v>125194954</v>
       </c>
       <c r="B11" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1622,46 +1639,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592598</v>
+        <v>592687</v>
       </c>
       <c r="R11" t="n">
-        <v>6984734</v>
+        <v>6984736</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194946</v>
+        <v>125194959</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>91410</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592735</v>
+        <v>592555</v>
       </c>
       <c r="R12" t="n">
-        <v>6984754</v>
+        <v>6984742</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194952</v>
+        <v>125194957</v>
       </c>
       <c r="B13" t="n">
-        <v>96979</v>
+        <v>79927</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592763</v>
+        <v>592680</v>
       </c>
       <c r="R13" t="n">
-        <v>6984830</v>
+        <v>6984734</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194960</v>
+        <v>125194961</v>
       </c>
       <c r="B2" t="n">
-        <v>56714</v>
+        <v>91030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,46 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592598</v>
+        <v>592738</v>
       </c>
       <c r="R2" t="n">
-        <v>6984734</v>
+        <v>6984923</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -789,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194950</v>
+        <v>125194954</v>
       </c>
       <c r="B3" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,42 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592775</v>
+        <v>592687</v>
       </c>
       <c r="R3" t="n">
-        <v>6984833</v>
+        <v>6984736</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -899,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194961</v>
+        <v>125194946</v>
       </c>
       <c r="B4" t="n">
-        <v>91030</v>
+        <v>74901</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592738</v>
+        <v>592735</v>
       </c>
       <c r="R4" t="n">
-        <v>6984923</v>
+        <v>6984754</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1103,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194946</v>
+        <v>125194960</v>
       </c>
       <c r="B6" t="n">
-        <v>74901</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,34 +1099,46 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592735</v>
+        <v>592598</v>
       </c>
       <c r="R6" t="n">
-        <v>6984754</v>
+        <v>6984734</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1205,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194964</v>
+        <v>125194948</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,34 +1213,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592722</v>
+        <v>592721</v>
       </c>
       <c r="R7" t="n">
-        <v>6984773</v>
+        <v>6984921</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1281,6 +1278,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1309,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194965</v>
+        <v>125194959</v>
       </c>
       <c r="B8" t="n">
-        <v>96227</v>
+        <v>91410</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1319,25 +1321,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bollvitmossa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1344,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592758</v>
+        <v>592555</v>
       </c>
       <c r="R8" t="n">
-        <v>6984821</v>
+        <v>6984742</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1409,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194963</v>
+        <v>125194950</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,34 +1422,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592734</v>
+        <v>592775</v>
       </c>
       <c r="R9" t="n">
-        <v>6984760</v>
+        <v>6984833</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194948</v>
+        <v>125194957</v>
       </c>
       <c r="B10" t="n">
-        <v>57513</v>
+        <v>79927</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1523,43 +1528,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592721</v>
+        <v>592680</v>
       </c>
       <c r="R10" t="n">
-        <v>6984921</v>
+        <v>6984734</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1592,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194954</v>
+        <v>125194965</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>96227</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1635,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592687</v>
+        <v>592758</v>
       </c>
       <c r="R11" t="n">
-        <v>6984736</v>
+        <v>6984821</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1725,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194959</v>
+        <v>125194964</v>
       </c>
       <c r="B12" t="n">
-        <v>91410</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,16 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592555</v>
+        <v>592722</v>
       </c>
       <c r="R12" t="n">
-        <v>6984742</v>
+        <v>6984773</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194957</v>
+        <v>125194963</v>
       </c>
       <c r="B13" t="n">
-        <v>79927</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1834,25 +1834,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592680</v>
+        <v>592734</v>
       </c>
       <c r="R13" t="n">
-        <v>6984734</v>
+        <v>6984760</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -1406,10 +1406,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194950</v>
+        <v>125194957</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79927</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,46 +1418,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6464</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592775</v>
+        <v>592680</v>
       </c>
       <c r="R9" t="n">
-        <v>6984833</v>
+        <v>6984734</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1516,10 +1508,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194957</v>
+        <v>125194950</v>
       </c>
       <c r="B10" t="n">
-        <v>79927</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1528,38 +1520,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592680</v>
+        <v>592775</v>
       </c>
       <c r="R10" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194961</v>
+        <v>125194963</v>
       </c>
       <c r="B2" t="n">
-        <v>91030</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592738</v>
+        <v>592734</v>
       </c>
       <c r="R2" t="n">
-        <v>6984923</v>
+        <v>6984760</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194954</v>
+        <v>125194961</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91030</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592687</v>
+        <v>592738</v>
       </c>
       <c r="R3" t="n">
-        <v>6984736</v>
+        <v>6984923</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194946</v>
+        <v>125194964</v>
       </c>
       <c r="B4" t="n">
-        <v>74901</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592735</v>
+        <v>592722</v>
       </c>
       <c r="R4" t="n">
-        <v>6984754</v>
+        <v>6984773</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194952</v>
+        <v>125194950</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>57666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,38 +993,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592763</v>
+        <v>592775</v>
       </c>
       <c r="R5" t="n">
-        <v>6984830</v>
+        <v>6984833</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194960</v>
+        <v>125194965</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>96227</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,50 +1103,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592598</v>
+        <v>592758</v>
       </c>
       <c r="R6" t="n">
-        <v>6984734</v>
+        <v>6984821</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1309,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194959</v>
+        <v>125194954</v>
       </c>
       <c r="B8" t="n">
-        <v>91410</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1325,16 +1321,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1344,10 +1345,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592555</v>
+        <v>592687</v>
       </c>
       <c r="R8" t="n">
-        <v>6984742</v>
+        <v>6984736</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1406,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194957</v>
+        <v>125194959</v>
       </c>
       <c r="B9" t="n">
-        <v>79927</v>
+        <v>91410</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1418,25 +1419,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Luddlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1446,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592680</v>
+        <v>592555</v>
       </c>
       <c r="R9" t="n">
-        <v>6984734</v>
+        <v>6984742</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1508,10 +1504,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194950</v>
+        <v>125194952</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>96979</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1520,46 +1516,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592775</v>
+        <v>592763</v>
       </c>
       <c r="R10" t="n">
-        <v>6984833</v>
+        <v>6984830</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1618,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194965</v>
+        <v>125194957</v>
       </c>
       <c r="B11" t="n">
-        <v>96227</v>
+        <v>79927</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1622,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592758</v>
+        <v>592680</v>
       </c>
       <c r="R11" t="n">
-        <v>6984821</v>
+        <v>6984734</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,10 +1708,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194964</v>
+        <v>125194946</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>74901</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1724,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592722</v>
+        <v>592735</v>
       </c>
       <c r="R12" t="n">
-        <v>6984773</v>
+        <v>6984754</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194963</v>
+        <v>125194960</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,34 +1826,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592734</v>
+        <v>592598</v>
       </c>
       <c r="R13" t="n">
-        <v>6984760</v>
+        <v>6984734</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194963</v>
+        <v>125194957</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>80064</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592734</v>
+        <v>592680</v>
       </c>
       <c r="R2" t="n">
-        <v>6984760</v>
+        <v>6984734</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194961</v>
+        <v>125194952</v>
       </c>
       <c r="B3" t="n">
-        <v>91030</v>
+        <v>97147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592738</v>
+        <v>592763</v>
       </c>
       <c r="R3" t="n">
-        <v>6984923</v>
+        <v>6984830</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194964</v>
+        <v>125194965</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>96395</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592722</v>
+        <v>592758</v>
       </c>
       <c r="R4" t="n">
-        <v>6984773</v>
+        <v>6984821</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194950</v>
+        <v>125194963</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +997,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592775</v>
+        <v>592734</v>
       </c>
       <c r="R5" t="n">
-        <v>6984833</v>
+        <v>6984760</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194965</v>
+        <v>125194950</v>
       </c>
       <c r="B6" t="n">
-        <v>96227</v>
+        <v>57793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1103,38 +1095,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2869</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592758</v>
+        <v>592775</v>
       </c>
       <c r="R6" t="n">
-        <v>6984821</v>
+        <v>6984833</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194948</v>
+        <v>125194960</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56828</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,16 +1209,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1226,22 +1226,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592721</v>
+        <v>592598</v>
       </c>
       <c r="R7" t="n">
-        <v>6984921</v>
+        <v>6984734</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1274,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194954</v>
+        <v>125194959</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>91570</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1321,21 +1323,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592687</v>
+        <v>592555</v>
       </c>
       <c r="R8" t="n">
-        <v>6984736</v>
+        <v>6984742</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194959</v>
+        <v>125194948</v>
       </c>
       <c r="B9" t="n">
-        <v>91410</v>
+        <v>57635</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1423,29 +1420,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592555</v>
+        <v>592721</v>
       </c>
       <c r="R9" t="n">
-        <v>6984742</v>
+        <v>6984921</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1478,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1504,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194952</v>
+        <v>125194954</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1516,25 +1528,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1544,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592763</v>
+        <v>592687</v>
       </c>
       <c r="R10" t="n">
-        <v>6984830</v>
+        <v>6984736</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194957</v>
+        <v>125194961</v>
       </c>
       <c r="B11" t="n">
-        <v>79927</v>
+        <v>91184</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1618,25 +1630,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592680</v>
+        <v>592738</v>
       </c>
       <c r="R11" t="n">
-        <v>6984734</v>
+        <v>6984923</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194946</v>
+        <v>125194964</v>
       </c>
       <c r="B12" t="n">
-        <v>74901</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1724,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592735</v>
+        <v>592722</v>
       </c>
       <c r="R12" t="n">
-        <v>6984754</v>
+        <v>6984773</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194960</v>
+        <v>125194946</v>
       </c>
       <c r="B13" t="n">
-        <v>56714</v>
+        <v>75025</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1826,46 +1838,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592598</v>
+        <v>592735</v>
       </c>
       <c r="R13" t="n">
-        <v>6984734</v>
+        <v>6984754</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194957</v>
+        <v>125194952</v>
       </c>
       <c r="B2" t="n">
-        <v>80064</v>
+        <v>97147</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592680</v>
+        <v>592763</v>
       </c>
       <c r="R2" t="n">
-        <v>6984734</v>
+        <v>6984830</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194952</v>
+        <v>125194957</v>
       </c>
       <c r="B3" t="n">
-        <v>97147</v>
+        <v>80064</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592763</v>
+        <v>592680</v>
       </c>
       <c r="R3" t="n">
-        <v>6984830</v>
+        <v>6984734</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194950</v>
+        <v>125194960</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
+        <v>56828</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,29 +1099,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1131,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592775</v>
+        <v>592598</v>
       </c>
       <c r="R6" t="n">
-        <v>6984833</v>
+        <v>6984734</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1193,10 +1197,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194960</v>
+        <v>125194950</v>
       </c>
       <c r="B7" t="n">
-        <v>56828</v>
+        <v>57793</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,33 +1213,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592598</v>
+        <v>592775</v>
       </c>
       <c r="R7" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194952</v>
+        <v>125194946</v>
       </c>
       <c r="B2" t="n">
-        <v>97147</v>
+        <v>75025</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592763</v>
+        <v>592735</v>
       </c>
       <c r="R2" t="n">
-        <v>6984830</v>
+        <v>6984754</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194957</v>
+        <v>125194952</v>
       </c>
       <c r="B3" t="n">
-        <v>80064</v>
+        <v>97147</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592680</v>
+        <v>592763</v>
       </c>
       <c r="R3" t="n">
-        <v>6984734</v>
+        <v>6984830</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194965</v>
+        <v>125194961</v>
       </c>
       <c r="B4" t="n">
-        <v>96395</v>
+        <v>91184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592758</v>
+        <v>592738</v>
       </c>
       <c r="R4" t="n">
-        <v>6984821</v>
+        <v>6984923</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194963</v>
+        <v>125194950</v>
       </c>
       <c r="B5" t="n">
-        <v>78947</v>
+        <v>57793</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,34 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592734</v>
+        <v>592775</v>
       </c>
       <c r="R5" t="n">
-        <v>6984760</v>
+        <v>6984833</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1083,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194960</v>
+        <v>125194954</v>
       </c>
       <c r="B6" t="n">
-        <v>56828</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,46 +1107,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592598</v>
+        <v>592687</v>
       </c>
       <c r="R6" t="n">
-        <v>6984734</v>
+        <v>6984736</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1197,10 +1193,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194950</v>
+        <v>125194964</v>
       </c>
       <c r="B7" t="n">
-        <v>57793</v>
+        <v>78947</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1213,42 +1209,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592775</v>
+        <v>592722</v>
       </c>
       <c r="R7" t="n">
-        <v>6984833</v>
+        <v>6984773</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1307,10 +1295,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194959</v>
+        <v>125194948</v>
       </c>
       <c r="B8" t="n">
-        <v>91570</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,29 +1311,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592555</v>
+        <v>592721</v>
       </c>
       <c r="R8" t="n">
-        <v>6984742</v>
+        <v>6984921</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1378,6 +1376,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194948</v>
+        <v>125194965</v>
       </c>
       <c r="B9" t="n">
-        <v>57635</v>
+        <v>96395</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1416,43 +1419,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592721</v>
+        <v>592758</v>
       </c>
       <c r="R9" t="n">
-        <v>6984921</v>
+        <v>6984821</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1485,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1509,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194954</v>
+        <v>125194959</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>91570</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1525,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592687</v>
+        <v>592555</v>
       </c>
       <c r="R10" t="n">
-        <v>6984736</v>
+        <v>6984742</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1618,10 +1606,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194961</v>
+        <v>125194957</v>
       </c>
       <c r="B11" t="n">
-        <v>91184</v>
+        <v>80064</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1618,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592738</v>
+        <v>592680</v>
       </c>
       <c r="R11" t="n">
-        <v>6984923</v>
+        <v>6984734</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1720,7 +1708,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194964</v>
+        <v>125194963</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1760,10 +1748,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592722</v>
+        <v>592734</v>
       </c>
       <c r="R12" t="n">
-        <v>6984773</v>
+        <v>6984760</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1822,10 +1810,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194946</v>
+        <v>125194960</v>
       </c>
       <c r="B13" t="n">
-        <v>75025</v>
+        <v>56828</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,34 +1826,46 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592735</v>
+        <v>592598</v>
       </c>
       <c r="R13" t="n">
-        <v>6984754</v>
+        <v>6984734</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -1091,10 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194954</v>
+        <v>125194948</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1107,34 +1107,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592687</v>
+        <v>592721</v>
       </c>
       <c r="R6" t="n">
-        <v>6984736</v>
+        <v>6984921</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1167,6 +1172,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194964</v>
+        <v>125194954</v>
       </c>
       <c r="B7" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1209,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592722</v>
+        <v>592687</v>
       </c>
       <c r="R7" t="n">
-        <v>6984773</v>
+        <v>6984736</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1295,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194948</v>
+        <v>125194965</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
+        <v>96395</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1307,43 +1317,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592721</v>
+        <v>592758</v>
       </c>
       <c r="R8" t="n">
-        <v>6984921</v>
+        <v>6984821</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1376,11 +1381,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194965</v>
+        <v>125194964</v>
       </c>
       <c r="B9" t="n">
-        <v>96395</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,25 +1419,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592758</v>
+        <v>592722</v>
       </c>
       <c r="R9" t="n">
-        <v>6984821</v>
+        <v>6984773</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194946</v>
+        <v>125194959</v>
       </c>
       <c r="B2" t="n">
-        <v>75025</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +705,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592735</v>
+        <v>592555</v>
       </c>
       <c r="R2" t="n">
-        <v>6984754</v>
+        <v>6984742</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,37 +767,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194952</v>
+        <v>125194964</v>
       </c>
       <c r="B3" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +802,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592763</v>
+        <v>592722</v>
       </c>
       <c r="R3" t="n">
-        <v>6984830</v>
+        <v>6984773</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -879,15 +864,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194961</v>
+        <v>125194963</v>
       </c>
       <c r="B4" t="n">
-        <v>91184</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +875,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +899,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592738</v>
+        <v>592734</v>
       </c>
       <c r="R4" t="n">
-        <v>6984923</v>
+        <v>6984760</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,58 +961,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194950</v>
+        <v>125194965</v>
       </c>
       <c r="B5" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592775</v>
+        <v>592758</v>
       </c>
       <c r="R5" t="n">
-        <v>6984833</v>
+        <v>6984821</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1091,55 +1058,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125194948</v>
+        <v>125194957</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80106</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592721</v>
+        <v>592680</v>
       </c>
       <c r="R6" t="n">
-        <v>6984921</v>
+        <v>6984734</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1172,11 +1129,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1203,37 +1155,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125194954</v>
+        <v>125194952</v>
       </c>
       <c r="B7" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1190,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592687</v>
+        <v>592763</v>
       </c>
       <c r="R7" t="n">
-        <v>6984736</v>
+        <v>6984830</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,37 +1252,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125194965</v>
+        <v>125194961</v>
       </c>
       <c r="B8" t="n">
-        <v>96395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91238</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1345,10 +1287,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592758</v>
+        <v>592738</v>
       </c>
       <c r="R8" t="n">
-        <v>6984821</v>
+        <v>6984923</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1407,15 +1349,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125194964</v>
+        <v>125194954</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1423,21 +1360,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1447,10 +1384,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592722</v>
+        <v>592687</v>
       </c>
       <c r="R9" t="n">
-        <v>6984773</v>
+        <v>6984736</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1509,15 +1446,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194959</v>
+        <v>125194960</v>
       </c>
       <c r="B10" t="n">
-        <v>91570</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1525,29 +1457,46 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6040186</v>
+        <v>102612</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592555</v>
+        <v>592598</v>
       </c>
       <c r="R10" t="n">
-        <v>6984742</v>
+        <v>6984734</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1606,50 +1555,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194957</v>
+        <v>125194950</v>
       </c>
       <c r="B11" t="n">
-        <v>80064</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6464</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592680</v>
+        <v>592775</v>
       </c>
       <c r="R11" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1708,15 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125194963</v>
+        <v>125194946</v>
       </c>
       <c r="B12" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75066</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1724,21 +1671,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1748,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592734</v>
+        <v>592735</v>
       </c>
       <c r="R12" t="n">
-        <v>6984760</v>
+        <v>6984754</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1810,15 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125194960</v>
+        <v>125194948</v>
       </c>
       <c r="B13" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1826,16 +1768,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1843,29 +1785,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Ödingen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592598</v>
+        <v>592721</v>
       </c>
       <c r="R13" t="n">
-        <v>6984734</v>
+        <v>6984921</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1898,6 +1833,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125194959</v>
+        <v>125194964</v>
       </c>
       <c r="B2" t="n">
-        <v>91624</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -705,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592555</v>
+        <v>592722</v>
       </c>
       <c r="R2" t="n">
-        <v>6984742</v>
+        <v>6984773</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -767,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125194964</v>
+        <v>125194963</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -802,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592722</v>
+        <v>592734</v>
       </c>
       <c r="R3" t="n">
-        <v>6984773</v>
+        <v>6984760</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194963</v>
+        <v>125194959</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>91631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -875,21 +880,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592734</v>
+        <v>592555</v>
       </c>
       <c r="R4" t="n">
-        <v>6984760</v>
+        <v>6984742</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -964,7 +964,7 @@
         <v>125194965</v>
       </c>
       <c r="B5" t="n">
-        <v>96450</v>
+        <v>96457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1158,7 +1158,7 @@
         <v>125194952</v>
       </c>
       <c r="B7" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,7 +1255,7 @@
         <v>125194961</v>
       </c>
       <c r="B8" t="n">
-        <v>91238</v>
+        <v>91245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194960</v>
+        <v>125194950</v>
       </c>
       <c r="B10" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,33 +1457,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1493,10 +1489,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592598</v>
+        <v>592775</v>
       </c>
       <c r="R10" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1555,10 +1551,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194950</v>
+        <v>125194960</v>
       </c>
       <c r="B11" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1566,29 +1562,33 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592775</v>
+        <v>592598</v>
       </c>
       <c r="R11" t="n">
-        <v>6984833</v>
+        <v>6984734</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -869,27 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125194959</v>
+        <v>125194965</v>
       </c>
       <c r="B4" t="n">
-        <v>91631</v>
+        <v>96457</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>2869</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -899,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592555</v>
+        <v>592758</v>
       </c>
       <c r="R4" t="n">
-        <v>6984742</v>
+        <v>6984821</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -961,32 +966,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125194965</v>
+        <v>125194959</v>
       </c>
       <c r="B5" t="n">
-        <v>96457</v>
+        <v>91631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bollvitmossa</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -996,10 +996,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592758</v>
+        <v>592555</v>
       </c>
       <c r="R5" t="n">
-        <v>6984821</v>
+        <v>6984742</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1446,10 +1446,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125194950</v>
+        <v>125194960</v>
       </c>
       <c r="B10" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1457,29 +1457,33 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1489,10 +1493,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592775</v>
+        <v>592598</v>
       </c>
       <c r="R10" t="n">
-        <v>6984833</v>
+        <v>6984734</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1551,10 +1555,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125194960</v>
+        <v>125194950</v>
       </c>
       <c r="B11" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1562,33 +1566,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1598,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592598</v>
+        <v>592775</v>
       </c>
       <c r="R11" t="n">
-        <v>6984734</v>
+        <v>6984833</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -1760,7 +1760,7 @@
         <v>125194948</v>
       </c>
       <c r="B13" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -1760,7 +1760,7 @@
         <v>125194948</v>
       </c>
       <c r="B13" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 19313-2025 artfynd.xlsx
+++ b/artfynd/A 19313-2025 artfynd.xlsx
@@ -1760,7 +1760,7 @@
         <v>125194948</v>
       </c>
       <c r="B13" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
